--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>IsTreasureSynergy</t>
+  </si>
+  <si>
     <t>RequireCount</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>羁绊描述</t>
   </si>
   <si>
+    <t>是否为宝物羁绊</t>
+  </si>
+  <si>
     <t>激活所需数量</t>
   </si>
   <si>
@@ -95,7 +101,25 @@
     <t>集齐日本三神器（八尺琼勾玉、天丛云剑、八咫镜），获得神之力量：全属性+20%，攻击时有20%概率造成三倍伤害</t>
   </si>
   <si>
-    <t>8,9,10</t>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>月神之力</t>
+  </si>
+  <si>
+    <t>集齐月神的三件宝物（月华玉璧、太阴弦月弓、月轮镜），获得月神的祝福：防御+30%，法术抗性+20%，生命恢复+5%</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>炎魔之怒</t>
+  </si>
+  <si>
+    <t>集齐炎魔的三件宝物（炎魔之心、炎魔之冠、炎魔之剑），获得炎魔的力量：攻击+30%，火伤害+50%，暴击率+15%</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
   </si>
 </sst>
 </file>
@@ -1070,20 +1094,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="6" max="6" width="97.875" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,10 +1120,11 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1118,92 +1144,160 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>9</v>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:9">
+    <row r="5" ht="15" customHeight="1" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
-        <v>3001</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1">
         <v>3004</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5002</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -59,6 +59,9 @@
     <t>EffectId</t>
   </si>
   <si>
+    <t>IconId</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t>羁绊效果ID</t>
   </si>
   <si>
+    <t>羁绊图标资源ID（-1表示无图标）</t>
+  </si>
+  <si>
     <t>三神器</t>
   </si>
   <si>
@@ -120,6 +126,24 @@
   </si>
   <si>
     <t>16,17,18</t>
+  </si>
+  <si>
+    <t>日月</t>
+  </si>
+  <si>
+    <t>场上有2名日月种族棋子时，全体日月棋子攻击力+10%，防御+10%</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>场上有2名法师职业棋子时，全体法师棋子法术强度+15%，冷却缩减+10%</t>
+  </si>
+  <si>
+    <t>103</t>
   </si>
 </sst>
 </file>
@@ -1094,21 +1118,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="97.875" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1123,8 +1148,9 @@
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
       <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,83 +1179,92 @@
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:10">
+    <row r="5" ht="15" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1238,26 +1273,29 @@
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1">
         <v>3004</v>
       </c>
+      <c r="K5" s="1">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:10">
+    <row r="6" ht="15" customHeight="1" spans="1:11">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1266,26 +1304,29 @@
         <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1">
-        <v>5001</v>
+        <v>5101</v>
+      </c>
+      <c r="K6" s="1">
+        <v>-1</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:10">
+    <row r="7" ht="15" customHeight="1" spans="1:11">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1294,10 +1335,75 @@
         <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J7" s="1">
-        <v>5002</v>
+        <v>5102</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:11">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>16001</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:11">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="1">
+        <v>7002</v>
+      </c>
+      <c r="K9" s="1">
+        <v>16002</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -156,14 +156,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,148 +612,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -41,9 +41,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -53,12 +50,12 @@
     <t>RequireCount</t>
   </si>
   <si>
-    <t>RequireIds</t>
-  </si>
-  <si>
     <t>EffectId</t>
   </si>
   <si>
+    <t>ApplyScope</t>
+  </si>
+  <si>
     <t>IconId</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>羁绊ID</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>羁绊名称</t>
   </si>
   <si>
-    <t>羁绊类型</t>
-  </si>
-  <si>
     <t>羁绊描述</t>
   </si>
   <si>
@@ -92,58 +83,67 @@
     <t>激活所需数量</t>
   </si>
   <si>
-    <t>需要的物品ID列表</t>
-  </si>
-  <si>
     <t>羁绊效果ID</t>
   </si>
   <si>
+    <t>应用范围</t>
+  </si>
+  <si>
     <t>羁绊图标资源ID（-1表示无图标）</t>
   </si>
   <si>
+    <t>日月</t>
+  </si>
+  <si>
+    <t>场上有2名日月种族棋子时，全体日月棋子攻击力+10%，防御+10%</t>
+  </si>
+  <si>
+    <t>污染生物</t>
+  </si>
+  <si>
+    <t>场上有2名污染生物种族棋子时，全体污染生物棋子获得伤害加深效果</t>
+  </si>
+  <si>
+    <t>灵魂</t>
+  </si>
+  <si>
+    <t>场上有1名灵魂种族棋子时，该棋子获得灵魂之力加成</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>场上有1名射手职业棋子时，该棋子攻击距离+2，攻击力+10%</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>场上有2名法师职业棋子时，全体法师棋子法术强度+15%，冷却缩减+10%</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>场上有2名战士职业棋子时，全体战士棋子攻击力+15%，护甲+10%</t>
+  </si>
+  <si>
     <t>三神器</t>
   </si>
   <si>
     <t>集齐日本三神器（八尺琼勾玉、天丛云剑、八咫镜），获得神之力量：全属性+20%，攻击时有20%概率造成三倍伤害</t>
   </si>
   <si>
-    <t>7,8,9</t>
-  </si>
-  <si>
     <t>月神之力</t>
   </si>
   <si>
     <t>集齐月神的三件宝物（月华玉璧、太阴弦月弓、月轮镜），获得月神的祝福：防御+30%，法术抗性+20%，生命恢复+5%</t>
   </si>
   <si>
-    <t>13,14,15</t>
-  </si>
-  <si>
     <t>炎魔之怒</t>
   </si>
   <si>
     <t>集齐炎魔的三件宝物（炎魔之心、炎魔之冠、炎魔之剑），获得炎魔的力量：攻击+30%，火伤害+50%，暴击率+15%</t>
-  </si>
-  <si>
-    <t>16,17,18</t>
-  </si>
-  <si>
-    <t>日月</t>
-  </si>
-  <si>
-    <t>场上有2名日月种族棋子时，全体日月棋子攻击力+10%，防御+10%</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>场上有2名法师职业棋子时，全体法师棋子法术强度+15%，冷却缩减+10%</t>
-  </si>
-  <si>
-    <t>103</t>
   </si>
 </sst>
 </file>
@@ -156,7 +156,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,157 +619,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1111,22 +1115,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1139,11 +1143,10 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1166,237 +1169,325 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:11">
+    <row r="5" ht="15" customHeight="1" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
+        <v>4004</v>
+      </c>
+      <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="J5" s="1">
-        <v>3004</v>
-      </c>
-      <c r="K5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:11">
+    <row r="6" ht="15" customHeight="1" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
+        <v>4006</v>
+      </c>
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="J6" s="1">
-        <v>5101</v>
-      </c>
-      <c r="K6" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:11">
+    <row r="7" ht="15" customHeight="1" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>4007</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>5102</v>
-      </c>
-      <c r="K7" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:11">
+    <row r="8" ht="15" customHeight="1" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
       <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>35</v>
+        <v>4009</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
       </c>
       <c r="J8" s="1">
-        <v>7001</v>
-      </c>
-      <c r="K8" s="1">
-        <v>16001</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:11">
+    <row r="9" ht="15" customHeight="1" spans="1:10">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4005</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>103</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4008</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:10">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>201</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4001</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:10">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>202</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
         <v>3</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H12" s="1">
+        <v>4002</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:10">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>203</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="1">
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4003</v>
+      </c>
+      <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="1">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="1">
-        <v>7002</v>
-      </c>
-      <c r="K9" s="1">
-        <v>16002</v>
+      <c r="J13" s="1">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -156,14 +156,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,148 +612,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1116,7 +1109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1126,7 +1119,7 @@
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="10.6296296296296" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1146,7 +1139,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="28.8" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>-1</v>
+        <v>16001</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:10">
@@ -1291,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>-1</v>
+        <v>16002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:10">
@@ -1319,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>-1</v>
+        <v>16003</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
@@ -1347,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="1">
-        <v>-1</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:10">
@@ -1375,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1">
-        <v>-1</v>
+        <v>16005</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:10">
@@ -1403,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1">
-        <v>-1</v>
+        <v>16006</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:10">

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
     <t>羁绊效果ID</t>
   </si>
   <si>
-    <t>应用范围</t>
+    <t>应用范围（0表示只对携带者生效）</t>
   </si>
   <si>
     <t>羁绊图标资源ID（-1表示无图标）</t>
@@ -1109,7 +1109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1119,7 +1119,7 @@
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="29.75" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1139,7 +1139,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="28.8" spans="1:10">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>4004</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
         <v>16001</v>
@@ -1281,7 +1281,7 @@
         <v>4006</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>16002</v>
@@ -1309,7 +1309,7 @@
         <v>4007</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
         <v>16003</v>
@@ -1337,7 +1337,7 @@
         <v>4009</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <v>16004</v>
@@ -1365,7 +1365,7 @@
         <v>4005</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
         <v>16005</v>
@@ -1393,7 +1393,7 @@
         <v>4008</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
         <v>16006</v>

--- a/AAAGameData/DataTables/SynergyTable.xlsx
+++ b/AAAGameData/DataTables/SynergyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1109,7 +1109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1199,7 +1199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" ht="28.8" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
